--- a/1-运维服务目录/0102-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/0102-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22155" windowHeight="13980" tabRatio="954" activeTab="5"/>
+    <workbookView windowWidth="20385" windowHeight="13215" tabRatio="954" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="服务目录" sheetId="8" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="109">
   <si>
     <t>组织级运维服务目录</t>
   </si>
@@ -303,6 +303,81 @@
     </r>
   </si>
   <si>
+    <t>服务报告周期</t>
+  </si>
+  <si>
+    <t>月度/季度/半年或年度</t>
+  </si>
+  <si>
+    <t>服务方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程或现场 </t>
+  </si>
+  <si>
+    <t>服务时间</t>
+  </si>
+  <si>
+    <t>7*24 或 5*8</t>
+  </si>
+  <si>
+    <t>交付成果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">《巡检记录表》《故障处理记录》 《运维服务报告》 </t>
+  </si>
+  <si>
+    <t>主机运维服务（040202）</t>
+  </si>
+  <si>
+    <t>主机运维服务</t>
+  </si>
+  <si>
+    <t>040202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">面向主机设备进行的例行检查及状态监控、响应支持、故障处理、性能优化等服务 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">保障和提升主机的可用性 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">计算机设备中的中型机、小型机、PC服务器等 </t>
+  </si>
+  <si>
+    <t>1、服务器硬件状态检查；</t>
+  </si>
+  <si>
+    <t>2、服务器硬件安装与调整；</t>
+  </si>
+  <si>
+    <t>3、对服务器性能进行监控；</t>
+  </si>
+  <si>
+    <t>4、服务器进程与服务检查；</t>
+  </si>
+  <si>
+    <t>5、服务器磁盘空间检查；</t>
+  </si>
+  <si>
+    <t>6、服务器系统漏洞修补；</t>
+  </si>
+  <si>
+    <t>7、系统配置与变更管理；</t>
+  </si>
+  <si>
+    <t>8、系统垃圾清理；</t>
+  </si>
+  <si>
+    <t>9、对客户申报的故障及时进行排查处理；</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10、按客户内部工作规范和流程的要求，完成客户领导交办的其它相关工作。 </t>
+  </si>
+  <si>
+    <t>巡检：每天/每周/每月或双方协定；</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -324,81 +399,6 @@
       </rPr>
       <t xml:space="preserve">                      90                                   48</t>
     </r>
-  </si>
-  <si>
-    <t>服务报告周期</t>
-  </si>
-  <si>
-    <t>月度/季度/半年或年度</t>
-  </si>
-  <si>
-    <t>服务方式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">远程或现场 </t>
-  </si>
-  <si>
-    <t>服务时间</t>
-  </si>
-  <si>
-    <t>7*24 或 5*8</t>
-  </si>
-  <si>
-    <t>交付成果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《巡检记录表》《故障处理记录》 《运维服务报告》 </t>
-  </si>
-  <si>
-    <t>主机运维服务（040202）</t>
-  </si>
-  <si>
-    <t>主机运维服务</t>
-  </si>
-  <si>
-    <t>040202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">面向主机设备进行的例行检查及状态监控、响应支持、故障处理、性能优化等服务 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">保障和提升主机的可用性 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">计算机设备中的中型机、小型机、PC服务器等 </t>
-  </si>
-  <si>
-    <t>1、服务器硬件状态检查；</t>
-  </si>
-  <si>
-    <t>2、服务器硬件安装与调整；</t>
-  </si>
-  <si>
-    <t>3、对服务器性能进行监控；</t>
-  </si>
-  <si>
-    <t>4、服务器进程与服务检查；</t>
-  </si>
-  <si>
-    <t>5、服务器磁盘空间检查；</t>
-  </si>
-  <si>
-    <t>6、服务器系统漏洞修补；</t>
-  </si>
-  <si>
-    <t>7、系统配置与变更管理；</t>
-  </si>
-  <si>
-    <t>8、系统垃圾清理；</t>
-  </si>
-  <si>
-    <t>9、对客户申报的故障及时进行排查处理；</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10、按客户内部工作规范和流程的要求，完成客户领导交办的其它相关工作。 </t>
-  </si>
-  <si>
-    <t>巡检：每天/每周/每月或双方协定；</t>
   </si>
   <si>
     <t>其他硬件运维服务（040299）</t>
@@ -1706,7 +1706,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="23.8833333333333" customWidth="1"/>
@@ -1862,41 +1862,35 @@
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:2">
-      <c r="A22" s="7"/>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:2">
-      <c r="A26" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1898,7 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A10:A16"/>
-    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1925,7 +1919,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2"/>
     </row>
@@ -1952,7 +1946,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:2">
@@ -1960,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:2">
@@ -1968,7 +1962,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:2">
@@ -1976,7 +1970,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:2">
@@ -1990,7 +1984,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:2">
@@ -1998,61 +1992,61 @@
         <v>29</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:2">
       <c r="A11" s="6"/>
       <c r="B11" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:2">
       <c r="A12" s="6"/>
       <c r="B12" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:2">
       <c r="A13" s="6"/>
       <c r="B13" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:2">
       <c r="A14" s="6"/>
       <c r="B14" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:2">
       <c r="A15" s="6"/>
       <c r="B15" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:2">
       <c r="A16" s="6"/>
       <c r="B16" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:2">
       <c r="A17" s="6"/>
       <c r="B17" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:2">
       <c r="A18" s="6"/>
       <c r="B18" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:2">
       <c r="A19" s="7"/>
       <c r="B19" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:2">
@@ -2060,7 +2054,7 @@
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:2">
@@ -2092,39 +2086,39 @@
     <row r="25" ht="16.5" customHeight="1" spans="1:2">
       <c r="A25" s="7"/>
       <c r="B25" s="8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:2">
       <c r="A26" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:2">
       <c r="A27" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:2">
       <c r="A28" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:2">
       <c r="A29" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2289,39 +2283,39 @@
     <row r="20" ht="18.75" customHeight="1" spans="1:2">
       <c r="A20" s="7"/>
       <c r="B20" s="8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:2">
       <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:2">
       <c r="A22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2498,39 +2492,39 @@
     <row r="22" ht="18" customHeight="1" spans="1:2">
       <c r="A22" s="7"/>
       <c r="B22" s="8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:2">
       <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2707,36 +2701,36 @@
     <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="7"/>
       <c r="B22" s="8" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>108</v>
